--- a/tools/encounters/Grafted_Encounter_Tables.xlsx
+++ b/tools/encounters/Grafted_Encounter_Tables.xlsx
@@ -14199,7 +14199,7 @@
       </c>
       <c r="O258" s="29" t="inlineStr">
         <is>
-          <t>Exploud</t>
+          <t>Gliscor</t>
         </is>
       </c>
     </row>
